--- a/data/excel/Administration_RevenueManagement_SupplierCommissionRule.xlsx
+++ b/data/excel/Administration_RevenueManagement_SupplierCommissionRule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kumar.gaurav\git\V12StagingB2C\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E66A040-7B01-43CD-BED4-69105871AAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCDF8C3-5820-41E8-A053-7C25C4CEB043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="145">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -461,10 +461,7 @@
     <t>9@6C6535C</t>
   </si>
   <si>
-    <t>ankur_ql</t>
-  </si>
-  <si>
-    <t>Ankur@123456</t>
+    <t>EE6B4B@E7</t>
   </si>
 </sst>
 </file>
@@ -565,7 +562,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -593,6 +590,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4279,7 +4282,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>68</v>
       </c>
@@ -4292,17 +4295,17 @@
       <c r="D2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="I2" t="s">
         <v>120</v>
@@ -4456,7 +4459,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="15">
+  <dataValidations count="14">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{D0FA302E-1612-4AD7-AEE8-4BB3738CCFCE}">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
@@ -4475,14 +4478,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2" xr:uid="{37C59080-B9AE-41FE-8BBA-FE0A84166E04}">
       <formula1>"Base Fare,Base Fare + YQ,Base Fare + YQ + YR,Base Fare + YR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{FE85240B-5CD4-4F99-9169-D28FD4D6E651}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{8183CEB8-3D65-4D0A-A791-6C9A79066DA6}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{1EA2AE97-CA36-460B-ADE9-C7F2E2799D1F}">
-      <formula1>"//v12staging/backoffice/,//xchangev12/backoffice/"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{CDF66741-DBDB-4A89-927C-DBA05C1A6D20}">
-      <formula1>"Piyush_ql,ankur_ql"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2" xr:uid="{3552E0EB-B756-4CDF-B67D-153C74833260}">
       <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
@@ -4499,10 +4496,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{8B18591A-6D38-40B9-8E23-B9D353224783}">
       <formula1>"Gaurav Travel,Hotelbeds,Zara Travel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{998939AE-FA69-43CE-9BE0-07B0323781DB}">
-      <formula1>"Password@@12,Ankur@12345,9@6C6535C,Ankur@123456"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{51692F5D-2276-4012-AB63-E5417A686452}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{1E884529-8A43-45AB-A642-2CEB5385CB92}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{AECA10B8-8B71-4DD1-9017-8510C9B5C767}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>